--- a/fact_competencia/outputs/06_historial_entrenamiento.xlsx
+++ b/fact_competencia/outputs/06_historial_entrenamiento.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -567,7 +567,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>1.040404183393313</v>
+        <v>1.040404183393314</v>
       </c>
       <c r="C9" t="n">
         <v>1.041416199205669</v>
@@ -618,7 +618,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>1.02431208200731</v>
+        <v>1.024312082007309</v>
       </c>
       <c r="C12" t="n">
         <v>1.0259548344484</v>
@@ -737,7 +737,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.9875604399170339</v>
+        <v>0.9875604399170338</v>
       </c>
       <c r="C19" t="n">
         <v>0.9904382547237039</v>
@@ -774,7 +774,7 @@
         <v>0.9771543944661615</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9803602219276247</v>
+        <v>0.9803602219276248</v>
       </c>
       <c r="D21" t="n">
         <v>0.7779447115384616</v>
@@ -805,7 +805,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.9667718382169266</v>
+        <v>0.9667718382169265</v>
       </c>
       <c r="C23" t="n">
         <v>0.9703031530257235</v>
@@ -856,7 +856,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.9512422169678362</v>
+        <v>0.9512422169678363</v>
       </c>
       <c r="C26" t="n">
         <v>0.9552648531685051</v>
@@ -876,7 +876,7 @@
         <v>0.9460798852992917</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9502686539857816</v>
+        <v>0.9502686539857815</v>
       </c>
       <c r="D27" t="n">
         <v>0.7872596153846154</v>
@@ -992,7 +992,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>0.9102802969165089</v>
+        <v>0.9102802969165088</v>
       </c>
       <c r="C34" t="n">
         <v>0.9156935959833901</v>
@@ -1077,10 +1077,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>0.8853167880231505</v>
+        <v>0.8853167880231504</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8916907160803517</v>
+        <v>0.8916907160803516</v>
       </c>
       <c r="D39" t="n">
         <v>0.78515625</v>
@@ -1097,7 +1097,7 @@
         <v>0.8804123307970654</v>
       </c>
       <c r="C40" t="n">
-        <v>0.8869877255503912</v>
+        <v>0.8869877255503911</v>
       </c>
       <c r="D40" t="n">
         <v>0.7848557692307693</v>
@@ -1148,7 +1148,7 @@
         <v>0.8659133108270562</v>
       </c>
       <c r="C43" t="n">
-        <v>0.8731112324201289</v>
+        <v>0.873111232420129</v>
       </c>
       <c r="D43" t="n">
         <v>0.7836538461538461</v>
@@ -1216,7 +1216,7 @@
         <v>0.8471530763512147</v>
       </c>
       <c r="C47" t="n">
-        <v>0.8552203215545794</v>
+        <v>0.8552203215545793</v>
       </c>
       <c r="D47" t="n">
         <v>0.7830528846153846</v>
@@ -1284,7 +1284,7 @@
         <v>0.8291441967679499</v>
       </c>
       <c r="C51" t="n">
-        <v>0.8381190949761267</v>
+        <v>0.8381190949761266</v>
       </c>
       <c r="D51" t="n">
         <v>0.7818509615384616</v>
@@ -1369,7 +1369,7 @@
         <v>0.8078146523796275</v>
       </c>
       <c r="C56" t="n">
-        <v>0.8179645041706491</v>
+        <v>0.817964504170649</v>
       </c>
       <c r="D56" t="n">
         <v>0.7821514423076923</v>
@@ -1386,7 +1386,7 @@
         <v>0.8037155485540566</v>
       </c>
       <c r="C57" t="n">
-        <v>0.8141042683204474</v>
+        <v>0.8141042683204472</v>
       </c>
       <c r="D57" t="n">
         <v>0.7821514423076923</v>
@@ -1417,7 +1417,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>0.7956891665411226</v>
+        <v>0.7956891665411225</v>
       </c>
       <c r="C59" t="n">
         <v>0.8065582681940987</v>
@@ -1468,7 +1468,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>0.7840847133839153</v>
+        <v>0.7840847133839152</v>
       </c>
       <c r="C62" t="n">
         <v>0.7956787254175712</v>
@@ -1590,7 +1590,7 @@
         <v>0.7590525395061433</v>
       </c>
       <c r="C69" t="n">
-        <v>0.7723380565785093</v>
+        <v>0.772338056578509</v>
       </c>
       <c r="D69" t="n">
         <v>0.7821514423076923</v>
@@ -1658,7 +1658,7 @@
         <v>0.7460154114214335</v>
       </c>
       <c r="C73" t="n">
-        <v>0.7602540799062261</v>
+        <v>0.760254079906226</v>
       </c>
       <c r="D73" t="n">
         <v>0.7824519230769231</v>
@@ -1675,7 +1675,7 @@
         <v>0.7428961438984742</v>
       </c>
       <c r="C74" t="n">
-        <v>0.7573704116718135</v>
+        <v>0.7573704116718136</v>
       </c>
       <c r="D74" t="n">
         <v>0.7827524038461539</v>
@@ -1689,7 +1689,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>0.7398317892472274</v>
+        <v>0.7398317892472273</v>
       </c>
       <c r="C75" t="n">
         <v>0.7545403757132511</v>
@@ -1709,7 +1709,7 @@
         <v>0.7368217366097711</v>
       </c>
       <c r="C76" t="n">
-        <v>0.751763266127888</v>
+        <v>0.7517632661278879</v>
       </c>
       <c r="D76" t="n">
         <v>0.7827524038461539</v>
@@ -1743,7 +1743,7 @@
         <v>0.7309619380934157</v>
       </c>
       <c r="C78" t="n">
-        <v>0.7463648679879475</v>
+        <v>0.7463648679879474</v>
       </c>
       <c r="D78" t="n">
         <v>0.7827524038461539</v>
@@ -1791,10 +1791,10 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>0.7225625629483768</v>
+        <v>0.7225625629483767</v>
       </c>
       <c r="C81" t="n">
-        <v>0.7386451438556888</v>
+        <v>0.738645143855689</v>
       </c>
       <c r="D81" t="n">
         <v>0.7827524038461539</v>
@@ -1808,7 +1808,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>0.7198639165197815</v>
+        <v>0.7198639165197814</v>
       </c>
       <c r="C82" t="n">
         <v>0.7361694272104859</v>
@@ -1910,7 +1910,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>0.7046792467564966</v>
+        <v>0.7046792467564967</v>
       </c>
       <c r="C88" t="n">
         <v>0.7222798765678646</v>
@@ -1930,7 +1930,7 @@
         <v>0.702308759351002</v>
       </c>
       <c r="C89" t="n">
-        <v>0.7201176670375836</v>
+        <v>0.7201176670375835</v>
       </c>
       <c r="D89" t="n">
         <v>0.7836538461538461</v>
@@ -1995,10 +1995,10 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>0.69325445648197</v>
+        <v>0.6932544564819699</v>
       </c>
       <c r="C93" t="n">
-        <v>0.7118732409418072</v>
+        <v>0.7118732409418074</v>
       </c>
       <c r="D93" t="n">
         <v>0.7842548076923077</v>
@@ -2066,7 +2066,7 @@
         <v>0.6848446078767277</v>
       </c>
       <c r="C97" t="n">
-        <v>0.7042345524289212</v>
+        <v>0.7042345524289213</v>
       </c>
       <c r="D97" t="n">
         <v>0.7836538461538461</v>
@@ -2117,7 +2117,7 @@
         <v>0.6789286650741629</v>
       </c>
       <c r="C100" t="n">
-        <v>0.6988706397881765</v>
+        <v>0.6988706397881764</v>
       </c>
       <c r="D100" t="n">
         <v>0.7836538461538461</v>
@@ -2131,7 +2131,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>0.6770269802660894</v>
+        <v>0.6770269802660893</v>
       </c>
       <c r="C101" t="n">
         <v>0.6971478567324342</v>
@@ -2165,7 +2165,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>0.6733243772282511</v>
+        <v>0.6733243772282512</v>
       </c>
       <c r="C103" t="n">
         <v>0.6937953237546984</v>
@@ -2182,7 +2182,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>0.6715219320611751</v>
+        <v>0.6715219320611749</v>
       </c>
       <c r="C104" t="n">
         <v>0.6921640299154225</v>
@@ -2250,7 +2250,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>0.6646205194431782</v>
+        <v>0.6646205194431786</v>
       </c>
       <c r="C108" t="n">
         <v>0.6859212138292051</v>
@@ -2352,7 +2352,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="n">
-        <v>0.6551156749581339</v>
+        <v>0.6551156749581337</v>
       </c>
       <c r="C114" t="n">
         <v>0.6773262274446811</v>
@@ -2474,7 +2474,7 @@
         <v>0.6451428110759687</v>
       </c>
       <c r="C121" t="n">
-        <v>0.6682979439725827</v>
+        <v>0.6682979439725825</v>
       </c>
       <c r="D121" t="n">
         <v>0.7875600961538461</v>
@@ -2488,7 +2488,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="n">
-        <v>0.6438050093526587</v>
+        <v>0.6438050093526586</v>
       </c>
       <c r="C122" t="n">
         <v>0.6670849949623073</v>
@@ -2539,7 +2539,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="n">
-        <v>0.6399098228759867</v>
+        <v>0.6399098228759866</v>
       </c>
       <c r="C125" t="n">
         <v>0.6635495395259152</v>
@@ -2610,7 +2610,7 @@
         <v>0.6349731351111967</v>
       </c>
       <c r="C129" t="n">
-        <v>0.6590585059653715</v>
+        <v>0.6590585059653714</v>
       </c>
       <c r="D129" t="n">
         <v>0.7875600961538461</v>
@@ -2624,7 +2624,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="n">
-        <v>0.6337816211820454</v>
+        <v>0.6337816211820453</v>
       </c>
       <c r="C130" t="n">
         <v>0.6579724536691848</v>
@@ -2641,7 +2641,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="n">
-        <v>0.6326062547674998</v>
+        <v>0.6326062547674997</v>
       </c>
       <c r="C131" t="n">
         <v>0.656900205540482</v>
@@ -2661,7 +2661,7 @@
         <v>0.6314465965849555</v>
       </c>
       <c r="C132" t="n">
-        <v>0.6558413417875741</v>
+        <v>0.6558413417875744</v>
       </c>
       <c r="D132" t="n">
         <v>0.7878605769230769</v>
@@ -2678,7 +2678,7 @@
         <v>0.6303022177027092</v>
       </c>
       <c r="C133" t="n">
-        <v>0.6547954533757598</v>
+        <v>0.6547954533757601</v>
       </c>
       <c r="D133" t="n">
         <v>0.7881610576923077</v>
@@ -2695,7 +2695,7 @@
         <v>0.6291726993743614</v>
       </c>
       <c r="C134" t="n">
-        <v>0.6537621418383307</v>
+        <v>0.6537621418383306</v>
       </c>
       <c r="D134" t="n">
         <v>0.7878605769230769</v>
@@ -2845,7 +2845,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="n">
-        <v>0.6196114879543917</v>
+        <v>0.6196114879543915</v>
       </c>
       <c r="C143" t="n">
         <v>0.6449675343729717</v>
@@ -2862,7 +2862,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="n">
-        <v>0.6186096622355118</v>
+        <v>0.6186096622355116</v>
       </c>
       <c r="C144" t="n">
         <v>0.6440402634264141</v>
@@ -2882,7 +2882,7 @@
         <v>0.6176187138196555</v>
       </c>
       <c r="C145" t="n">
-        <v>0.6431218286885053</v>
+        <v>0.6431218286885054</v>
       </c>
       <c r="D145" t="n">
         <v>0.7878605769230769</v>
@@ -2981,7 +2981,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>0.6118846307776806</v>
+        <v>0.6118846307776805</v>
       </c>
       <c r="C151" t="n">
         <v>0.6377812841363882</v>
@@ -3032,10 +3032,10 @@
         <v>153</v>
       </c>
       <c r="B154" t="n">
-        <v>0.6091410410206431</v>
+        <v>0.6091410410206433</v>
       </c>
       <c r="C154" t="n">
-        <v>0.6352088330271041</v>
+        <v>0.635208833027104</v>
       </c>
       <c r="D154" t="n">
         <v>0.7884615384615384</v>
@@ -3086,7 +3086,7 @@
         <v>0.6064705138989992</v>
       </c>
       <c r="C157" t="n">
-        <v>0.6326932295224476</v>
+        <v>0.6326932295224474</v>
       </c>
       <c r="D157" t="n">
         <v>0.7884615384615384</v>
@@ -3120,7 +3120,7 @@
         <v>0.6047276387815832</v>
       </c>
       <c r="C159" t="n">
-        <v>0.6310449545177353</v>
+        <v>0.6310449545177355</v>
       </c>
       <c r="D159" t="n">
         <v>0.7890625</v>
@@ -3134,7 +3134,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="n">
-        <v>0.6038667848716623</v>
+        <v>0.6038667848716625</v>
       </c>
       <c r="C160" t="n">
         <v>0.6302288695970115</v>
@@ -3168,10 +3168,10 @@
         <v>161</v>
       </c>
       <c r="B162" t="n">
-        <v>0.6021652037988026</v>
+        <v>0.6021652037988027</v>
       </c>
       <c r="C162" t="n">
-        <v>0.6286118872783858</v>
+        <v>0.6286118872783857</v>
       </c>
       <c r="D162" t="n">
         <v>0.7899639423076923</v>
@@ -3372,10 +3372,10 @@
         <v>173</v>
       </c>
       <c r="B174" t="n">
-        <v>0.5924412846594505</v>
+        <v>0.5924412846594503</v>
       </c>
       <c r="C174" t="n">
-        <v>0.6192675723046001</v>
+        <v>0.6192675723046002</v>
       </c>
       <c r="D174" t="n">
         <v>0.7911658653846154</v>
@@ -3409,7 +3409,7 @@
         <v>0.59088922087163</v>
       </c>
       <c r="C176" t="n">
-        <v>0.6177592670836596</v>
+        <v>0.6177592670836594</v>
       </c>
       <c r="D176" t="n">
         <v>0.7914663461538461</v>
@@ -3460,7 +3460,7 @@
         <v>0.5885917235422523</v>
       </c>
       <c r="C179" t="n">
-        <v>0.615517982745265</v>
+        <v>0.6155179827452649</v>
       </c>
       <c r="D179" t="n">
         <v>0.7920673076923077</v>
@@ -3477,7 +3477,7 @@
         <v>0.5878335427686873</v>
       </c>
       <c r="C180" t="n">
-        <v>0.6147761215669378</v>
+        <v>0.6147761215669377</v>
       </c>
       <c r="D180" t="n">
         <v>0.7920673076923077</v>
@@ -3494,7 +3494,7 @@
         <v>0.5870789865602848</v>
       </c>
       <c r="C181" t="n">
-        <v>0.6140367153247087</v>
+        <v>0.6140367153247086</v>
       </c>
       <c r="D181" t="n">
         <v>0.7920673076923077</v>
@@ -3579,7 +3579,7 @@
         <v>0.5833566394089716</v>
       </c>
       <c r="C186" t="n">
-        <v>0.6103733919912172</v>
+        <v>0.6103733919912173</v>
       </c>
       <c r="D186" t="n">
         <v>0.79296875</v>
@@ -3664,7 +3664,7 @@
         <v>0.5797088944665056</v>
       </c>
       <c r="C191" t="n">
-        <v>0.6067589057685053</v>
+        <v>0.6067589057685054</v>
       </c>
       <c r="D191" t="n">
         <v>0.79296875</v>
@@ -3698,7 +3698,7 @@
         <v>0.5782680594605085</v>
       </c>
       <c r="C193" t="n">
-        <v>0.6053247934731369</v>
+        <v>0.6053247934731371</v>
       </c>
       <c r="D193" t="n">
         <v>0.7935697115384616</v>
@@ -3715,7 +3715,7 @@
         <v>0.5775512152487674</v>
       </c>
       <c r="C194" t="n">
-        <v>0.6046099891567002</v>
+        <v>0.6046099891567003</v>
       </c>
       <c r="D194" t="n">
         <v>0.7935697115384616</v>
@@ -3817,7 +3817,7 @@
         <v>0.5732953558622484</v>
       </c>
       <c r="C200" t="n">
-        <v>0.6003492324637554</v>
+        <v>0.6003492324637555</v>
       </c>
       <c r="D200" t="n">
         <v>0.7941706730769231</v>
@@ -3831,7 +3831,7 @@
         <v>200</v>
       </c>
       <c r="B201" t="n">
-        <v>0.5725929190271611</v>
+        <v>0.5725929190271613</v>
       </c>
       <c r="C201" t="n">
         <v>0.599643321554008</v>
@@ -3865,7 +3865,7 @@
         <v>202</v>
       </c>
       <c r="B203" t="n">
-        <v>0.5711933469863165</v>
+        <v>0.5711933469863164</v>
       </c>
       <c r="C203" t="n">
         <v>0.5982347105356061</v>
@@ -3882,7 +3882,7 @@
         <v>203</v>
       </c>
       <c r="B204" t="n">
-        <v>0.5704960908938728</v>
+        <v>0.5704960908938727</v>
       </c>
       <c r="C204" t="n">
         <v>0.5975319302774159</v>
@@ -4072,7 +4072,7 @@
         <v>0.5629210941028163</v>
       </c>
       <c r="C215" t="n">
-        <v>0.589858011743939</v>
+        <v>0.5898580117439389</v>
       </c>
       <c r="D215" t="n">
         <v>0.7959735576923077</v>
@@ -4157,7 +4157,7 @@
         <v>0.5595250436426145</v>
       </c>
       <c r="C220" t="n">
-        <v>0.5863981003256902</v>
+        <v>0.5863981003256903</v>
       </c>
       <c r="D220" t="n">
         <v>0.796875</v>
@@ -4188,7 +4188,7 @@
         <v>221</v>
       </c>
       <c r="B222" t="n">
-        <v>0.5581732594950207</v>
+        <v>0.5581732594950206</v>
       </c>
       <c r="C222" t="n">
         <v>0.5850182038570667</v>
@@ -4259,7 +4259,7 @@
         <v>0.5554797105544713</v>
       </c>
       <c r="C226" t="n">
-        <v>0.5822647443177793</v>
+        <v>0.5822647443177792</v>
       </c>
       <c r="D226" t="n">
         <v>0.7971754807692307</v>
@@ -4358,10 +4358,10 @@
         <v>231</v>
       </c>
       <c r="B232" t="n">
-        <v>0.5514613493733063</v>
+        <v>0.5514613493733062</v>
       </c>
       <c r="C232" t="n">
-        <v>0.578149124153961</v>
+        <v>0.5781491241539611</v>
       </c>
       <c r="D232" t="n">
         <v>0.7977764423076923</v>
@@ -4378,7 +4378,7 @@
         <v>0.550793900786138</v>
       </c>
       <c r="C233" t="n">
-        <v>0.5774647868423612</v>
+        <v>0.5774647868423614</v>
       </c>
       <c r="D233" t="n">
         <v>0.7980769230769231</v>
@@ -4412,7 +4412,7 @@
         <v>0.549460787227063</v>
       </c>
       <c r="C235" t="n">
-        <v>0.5760974346265643</v>
+        <v>0.5760974346265642</v>
       </c>
       <c r="D235" t="n">
         <v>0.7983774038461539</v>
@@ -4545,10 +4545,10 @@
         <v>242</v>
       </c>
       <c r="B243" t="n">
-        <v>0.5441499276787651</v>
+        <v>0.544149927678765</v>
       </c>
       <c r="C243" t="n">
-        <v>0.5706452606023575</v>
+        <v>0.5706452606023574</v>
       </c>
       <c r="D243" t="n">
         <v>0.7998798076923077</v>
@@ -4684,7 +4684,7 @@
         <v>0.5388693287151137</v>
       </c>
       <c r="C251" t="n">
-        <v>0.5652205281110544</v>
+        <v>0.5652205281110543</v>
       </c>
       <c r="D251" t="n">
         <v>0.8001802884615384</v>
@@ -4718,7 +4718,7 @@
         <v>0.5375534404949719</v>
       </c>
       <c r="C253" t="n">
-        <v>0.5638687284850465</v>
+        <v>0.5638687284850464</v>
       </c>
       <c r="D253" t="n">
         <v>0.80078125</v>
@@ -4735,7 +4735,7 @@
         <v>0.5368961077890905</v>
       </c>
       <c r="C254" t="n">
-        <v>0.5631935024437851</v>
+        <v>0.563193502443785</v>
       </c>
       <c r="D254" t="n">
         <v>0.8010817307692307</v>
@@ -4752,7 +4752,7 @@
         <v>0.5362391778292385</v>
       </c>
       <c r="C255" t="n">
-        <v>0.5625187302924828</v>
+        <v>0.5625187302924827</v>
       </c>
       <c r="D255" t="n">
         <v>0.8013822115384616</v>
@@ -4936,10 +4936,10 @@
         <v>265</v>
       </c>
       <c r="B266" t="n">
-        <v>0.5290388751765174</v>
+        <v>0.5290388751765173</v>
       </c>
       <c r="C266" t="n">
-        <v>0.5551273056614153</v>
+        <v>0.5551273056614154</v>
       </c>
       <c r="D266" t="n">
         <v>0.8028846153846154</v>
@@ -5024,7 +5024,7 @@
         <v>0.5257814818742765</v>
       </c>
       <c r="C271" t="n">
-        <v>0.5517873000663932</v>
+        <v>0.5517873000663933</v>
       </c>
       <c r="D271" t="n">
         <v>0.8037860576923077</v>
@@ -5075,7 +5075,7 @@
         <v>0.5238316766488192</v>
       </c>
       <c r="C274" t="n">
-        <v>0.549789501870606</v>
+        <v>0.5497895018706059</v>
       </c>
       <c r="D274" t="n">
         <v>0.8040865384615384</v>
@@ -5242,10 +5242,10 @@
         <v>283</v>
       </c>
       <c r="B284" t="n">
-        <v>0.5173575845635535</v>
+        <v>0.5173575845635534</v>
       </c>
       <c r="C284" t="n">
-        <v>0.5431649117766213</v>
+        <v>0.5431649117766212</v>
       </c>
       <c r="D284" t="n">
         <v>0.8055889423076923</v>
@@ -5262,7 +5262,7 @@
         <v>0.5167123242113235</v>
       </c>
       <c r="C285" t="n">
-        <v>0.5425054455428637</v>
+        <v>0.5425054455428636</v>
       </c>
       <c r="D285" t="n">
         <v>0.8055889423076923</v>
@@ -5276,7 +5276,7 @@
         <v>285</v>
       </c>
       <c r="B286" t="n">
-        <v>0.5160674557993892</v>
+        <v>0.5160674557993891</v>
       </c>
       <c r="C286" t="n">
         <v>0.5418465289862244</v>
@@ -5313,7 +5313,7 @@
         <v>0.5147788951884014</v>
       </c>
       <c r="C288" t="n">
-        <v>0.5405303477489732</v>
+        <v>0.5405303477489731</v>
       </c>
       <c r="D288" t="n">
         <v>0.8055889423076923</v>
@@ -5480,10 +5480,10 @@
         <v>297</v>
       </c>
       <c r="B298" t="n">
-        <v>0.5083595714608989</v>
+        <v>0.5083595714608991</v>
       </c>
       <c r="C298" t="n">
-        <v>0.5339824938889608</v>
+        <v>0.5339824938889607</v>
       </c>
       <c r="D298" t="n">
         <v>0.8079927884615384</v>
@@ -5517,7 +5517,7 @@
         <v>0.5070803760904409</v>
       </c>
       <c r="C300" t="n">
-        <v>0.5326794997686548</v>
+        <v>0.5326794997686547</v>
       </c>
       <c r="D300" t="n">
         <v>0.8079927884615384</v>
@@ -5551,7 +5551,7 @@
         <v>0.5058027225458049</v>
       </c>
       <c r="C302" t="n">
-        <v>0.5313786745959546</v>
+        <v>0.5313786745959547</v>
       </c>
       <c r="D302" t="n">
         <v>0.8082932692307693</v>
@@ -5568,7 +5568,7 @@
         <v>0.5051644713333712</v>
       </c>
       <c r="C303" t="n">
-        <v>0.5307290709185042</v>
+        <v>0.5307290709185041</v>
       </c>
       <c r="D303" t="n">
         <v>0.80859375</v>
@@ -5653,7 +5653,7 @@
         <v>0.5019789230716383</v>
       </c>
       <c r="C308" t="n">
-        <v>0.5274890588477049</v>
+        <v>0.527489058847705</v>
       </c>
       <c r="D308" t="n">
         <v>0.8100961538461539</v>
@@ -5670,7 +5670,7 @@
         <v>0.5013429458428827</v>
       </c>
       <c r="C309" t="n">
-        <v>0.526842641619323</v>
+        <v>0.5268426416193229</v>
       </c>
       <c r="D309" t="n">
         <v>0.8103966346153846</v>
@@ -5684,7 +5684,7 @@
         <v>309</v>
       </c>
       <c r="B310" t="n">
-        <v>0.5007073428558323</v>
+        <v>0.5007073428558322</v>
       </c>
       <c r="C310" t="n">
         <v>0.5261967470210158</v>
@@ -5718,10 +5718,10 @@
         <v>311</v>
       </c>
       <c r="B312" t="n">
-        <v>0.4994372537876427</v>
+        <v>0.4994372537876426</v>
       </c>
       <c r="C312" t="n">
-        <v>0.5249065151763287</v>
+        <v>0.5249065151763286</v>
       </c>
       <c r="D312" t="n">
         <v>0.8103966346153846</v>
@@ -5738,7 +5738,7 @@
         <v>0.4988027647439824</v>
       </c>
       <c r="C313" t="n">
-        <v>0.5242621725142845</v>
+        <v>0.5242621725142844</v>
       </c>
       <c r="D313" t="n">
         <v>0.8103966346153846</v>
@@ -5769,7 +5769,7 @@
         <v>314</v>
       </c>
       <c r="B315" t="n">
-        <v>0.4975348901239762</v>
+        <v>0.4975348901239761</v>
       </c>
       <c r="C315" t="n">
         <v>0.5229750198057399</v>
@@ -5806,7 +5806,7 @@
         <v>0.4962684767006568</v>
       </c>
       <c r="C317" t="n">
-        <v>0.521689891604331</v>
+        <v>0.5216898916043312</v>
       </c>
       <c r="D317" t="n">
         <v>0.8106971153846154</v>
@@ -5854,7 +5854,7 @@
         <v>319</v>
       </c>
       <c r="B320" t="n">
-        <v>0.4943715699325534</v>
+        <v>0.4943715699325533</v>
       </c>
       <c r="C320" t="n">
         <v>0.5197659445812799</v>
@@ -5871,7 +5871,7 @@
         <v>320</v>
       </c>
       <c r="B321" t="n">
-        <v>0.4937399853082468</v>
+        <v>0.4937399853082467</v>
       </c>
       <c r="C321" t="n">
         <v>0.5191256159660437</v>
@@ -5922,10 +5922,10 @@
         <v>323</v>
       </c>
       <c r="B324" t="n">
-        <v>0.4918473642702404</v>
+        <v>0.4918473642702405</v>
       </c>
       <c r="C324" t="n">
-        <v>0.5172075504526406</v>
+        <v>0.5172075504526404</v>
       </c>
       <c r="D324" t="n">
         <v>0.8118990384615384</v>
@@ -6007,7 +6007,7 @@
         <v>328</v>
       </c>
       <c r="B329" t="n">
-        <v>0.4887000256311273</v>
+        <v>0.4887000256311272</v>
       </c>
       <c r="C329" t="n">
         <v>0.5140203371913028</v>
@@ -6024,10 +6024,10 @@
         <v>329</v>
       </c>
       <c r="B330" t="n">
-        <v>0.488071601445202</v>
+        <v>0.4880716014452019</v>
       </c>
       <c r="C330" t="n">
-        <v>0.513384303872098</v>
+        <v>0.5133843038720979</v>
       </c>
       <c r="D330" t="n">
         <v>0.8128004807692307</v>
@@ -6058,7 +6058,7 @@
         <v>331</v>
       </c>
       <c r="B332" t="n">
-        <v>0.4868157881241942</v>
+        <v>0.4868157881241943</v>
       </c>
       <c r="C332" t="n">
         <v>0.5121136252663635</v>
@@ -6129,7 +6129,7 @@
         <v>0.4843082775246681</v>
       </c>
       <c r="C336" t="n">
-        <v>0.509577750499889</v>
+        <v>0.5095777504998888</v>
       </c>
       <c r="D336" t="n">
         <v>0.8131009615384616</v>
@@ -6214,7 +6214,7 @@
         <v>0.4811815547254049</v>
       </c>
       <c r="C341" t="n">
-        <v>0.5064179990034281</v>
+        <v>0.5064179990034282</v>
       </c>
       <c r="D341" t="n">
         <v>0.8134014423076923</v>
@@ -6231,7 +6231,7 @@
         <v>0.4805572284356449</v>
       </c>
       <c r="C342" t="n">
-        <v>0.5057873739738631</v>
+        <v>0.505787373973863</v>
       </c>
       <c r="D342" t="n">
         <v>0.8134014423076923</v>
@@ -6282,7 +6282,7 @@
         <v>0.4786862846487252</v>
       </c>
       <c r="C345" t="n">
-        <v>0.503898118084888</v>
+        <v>0.5038981180848882</v>
       </c>
       <c r="D345" t="n">
         <v>0.8137019230769231</v>
@@ -6313,10 +6313,10 @@
         <v>346</v>
       </c>
       <c r="B347" t="n">
-        <v>0.4774406865792856</v>
+        <v>0.4774406865792857</v>
       </c>
       <c r="C347" t="n">
-        <v>0.5026407820930917</v>
+        <v>0.5026407820930918</v>
       </c>
       <c r="D347" t="n">
         <v>0.8137019230769231</v>
@@ -6333,7 +6333,7 @@
         <v>0.4768183979846213</v>
       </c>
       <c r="C348" t="n">
-        <v>0.5020127605965699</v>
+        <v>0.5020127605965697</v>
       </c>
       <c r="D348" t="n">
         <v>0.8137019230769231</v>
@@ -6435,7 +6435,7 @@
         <v>0.4730918558280162</v>
       </c>
       <c r="C354" t="n">
-        <v>0.498253621367551</v>
+        <v>0.4982536213675509</v>
       </c>
       <c r="D354" t="n">
         <v>0.8167067307692307</v>
@@ -6469,7 +6469,7 @@
         <v>0.4718524376452103</v>
       </c>
       <c r="C356" t="n">
-        <v>0.4970039836318887</v>
+        <v>0.4970039836318886</v>
       </c>
       <c r="D356" t="n">
         <v>0.8173076923076923</v>
@@ -6520,7 +6520,7 @@
         <v>0.4699959366829324</v>
       </c>
       <c r="C359" t="n">
-        <v>0.4951327137564535</v>
+        <v>0.4951327137564534</v>
       </c>
       <c r="D359" t="n">
         <v>0.8173076923076923</v>
@@ -6639,7 +6639,7 @@
         <v>0.4656766149710597</v>
       </c>
       <c r="C366" t="n">
-        <v>0.4907813170597806</v>
+        <v>0.4907813170597805</v>
       </c>
       <c r="D366" t="n">
         <v>0.8188100961538461</v>
@@ -6653,7 +6653,7 @@
         <v>366</v>
       </c>
       <c r="B367" t="n">
-        <v>0.4650610317032351</v>
+        <v>0.4650610317032352</v>
       </c>
       <c r="C367" t="n">
         <v>0.4901614003790475</v>
@@ -6792,7 +6792,7 @@
         <v>0.4601500616629579</v>
       </c>
       <c r="C375" t="n">
-        <v>0.4852176899601192</v>
+        <v>0.4852176899601191</v>
       </c>
       <c r="D375" t="n">
         <v>0.8206129807692307</v>
@@ -6809,7 +6809,7 @@
         <v>0.4595379513255445</v>
       </c>
       <c r="C376" t="n">
-        <v>0.4846017036906762</v>
+        <v>0.4846017036906761</v>
       </c>
       <c r="D376" t="n">
         <v>0.8206129807692307</v>
@@ -6823,7 +6823,7 @@
         <v>376</v>
       </c>
       <c r="B377" t="n">
-        <v>0.4589262442133188</v>
+        <v>0.4589262442133187</v>
       </c>
       <c r="C377" t="n">
         <v>0.4839861634038345</v>
@@ -6860,7 +6860,7 @@
         <v>0.4577040553010843</v>
       </c>
       <c r="C379" t="n">
-        <v>0.4827564299676894</v>
+        <v>0.4827564299676893</v>
       </c>
       <c r="D379" t="n">
         <v>0.8221153846153846</v>
@@ -6942,7 +6942,7 @@
         <v>383</v>
       </c>
       <c r="B384" t="n">
-        <v>0.4546559245739559</v>
+        <v>0.454655924573956</v>
       </c>
       <c r="C384" t="n">
         <v>0.4796900733852303</v>
@@ -6993,7 +6993,7 @@
         <v>386</v>
       </c>
       <c r="B387" t="n">
-        <v>0.4528322582961745</v>
+        <v>0.4528322582961744</v>
       </c>
       <c r="C387" t="n">
         <v>0.4778558428672106</v>
@@ -7027,7 +7027,7 @@
         <v>388</v>
       </c>
       <c r="B389" t="n">
-        <v>0.4516187318502349</v>
+        <v>0.451618731850235</v>
       </c>
       <c r="C389" t="n">
         <v>0.4766354014052132</v>
@@ -7112,7 +7112,7 @@
         <v>393</v>
       </c>
       <c r="B394" t="n">
-        <v>0.448593093937352</v>
+        <v>0.4485930939373519</v>
       </c>
       <c r="C394" t="n">
         <v>0.4735928289868194</v>
@@ -7129,7 +7129,7 @@
         <v>394</v>
       </c>
       <c r="B395" t="n">
-        <v>0.4479894114852151</v>
+        <v>0.447989411485215</v>
       </c>
       <c r="C395" t="n">
         <v>0.4729858071931532</v>
@@ -7180,7 +7180,7 @@
         <v>397</v>
       </c>
       <c r="B398" t="n">
-        <v>0.4461813559526595</v>
+        <v>0.4461813559526594</v>
       </c>
       <c r="C398" t="n">
         <v>0.4711677995200785</v>
@@ -7248,7 +7248,7 @@
         <v>401</v>
       </c>
       <c r="B402" t="n">
-        <v>0.4437778171246001</v>
+        <v>0.4437778171246</v>
       </c>
       <c r="C402" t="n">
         <v>0.468751084064605</v>
@@ -7299,7 +7299,7 @@
         <v>404</v>
       </c>
       <c r="B405" t="n">
-        <v>0.441980779155257</v>
+        <v>0.4419807791552569</v>
       </c>
       <c r="C405" t="n">
         <v>0.4669441760940598</v>
@@ -7421,7 +7421,7 @@
         <v>0.4378074627235188</v>
       </c>
       <c r="C412" t="n">
-        <v>0.4627476031322166</v>
+        <v>0.4627476031322165</v>
       </c>
       <c r="D412" t="n">
         <v>0.8275240384615384</v>
@@ -7455,7 +7455,7 @@
         <v>0.4366204117249497</v>
       </c>
       <c r="C414" t="n">
-        <v>0.4615537898636261</v>
+        <v>0.461553789863626</v>
       </c>
       <c r="D414" t="n">
         <v>0.828125</v>
@@ -7503,10 +7503,10 @@
         <v>416</v>
       </c>
       <c r="B417" t="n">
-        <v>0.4348444796123939</v>
+        <v>0.4348444796123938</v>
       </c>
       <c r="C417" t="n">
-        <v>0.4597675668582019</v>
+        <v>0.4597675668582018</v>
       </c>
       <c r="D417" t="n">
         <v>0.8287259615384616</v>
@@ -7537,7 +7537,7 @@
         <v>418</v>
       </c>
       <c r="B419" t="n">
-        <v>0.433663703401874</v>
+        <v>0.4336637034018739</v>
       </c>
       <c r="C419" t="n">
         <v>0.4585798124428497</v>
@@ -7591,7 +7591,7 @@
         <v>0.4318974497649193</v>
       </c>
       <c r="C422" t="n">
-        <v>0.4568028820309524</v>
+        <v>0.4568028820309525</v>
       </c>
       <c r="D422" t="n">
         <v>0.8299278846153846</v>
@@ -7656,10 +7656,10 @@
         <v>425</v>
       </c>
       <c r="B426" t="n">
-        <v>0.4295519152737148</v>
+        <v>0.4295519152737147</v>
       </c>
       <c r="C426" t="n">
-        <v>0.4544426515180678</v>
+        <v>0.4544426515180677</v>
       </c>
       <c r="D426" t="n">
         <v>0.8311298076923077</v>
@@ -7741,7 +7741,7 @@
         <v>430</v>
       </c>
       <c r="B431" t="n">
-        <v>0.4266358746701754</v>
+        <v>0.4266358746701753</v>
       </c>
       <c r="C431" t="n">
         <v>0.451507353082198</v>
@@ -7795,7 +7795,7 @@
         <v>0.4248950708539861</v>
       </c>
       <c r="C434" t="n">
-        <v>0.449754442625781</v>
+        <v>0.4497544426257808</v>
       </c>
       <c r="D434" t="n">
         <v>0.8338341346153846</v>
@@ -7914,7 +7914,7 @@
         <v>0.4208602063993754</v>
       </c>
       <c r="C441" t="n">
-        <v>0.4456894370324087</v>
+        <v>0.4456894370324086</v>
       </c>
       <c r="D441" t="n">
         <v>0.8374399038461539</v>
@@ -7931,7 +7931,7 @@
         <v>0.4202869911449941</v>
       </c>
       <c r="C442" t="n">
-        <v>0.4451116762969691</v>
+        <v>0.4451116762969692</v>
       </c>
       <c r="D442" t="n">
         <v>0.8374399038461539</v>
@@ -7945,7 +7945,7 @@
         <v>442</v>
       </c>
       <c r="B443" t="n">
-        <v>0.4197145960727171</v>
+        <v>0.4197145960727172</v>
       </c>
       <c r="C443" t="n">
         <v>0.4445346711319255</v>
@@ -7996,10 +7996,10 @@
         <v>445</v>
       </c>
       <c r="B446" t="n">
-        <v>0.4180024034087533</v>
+        <v>0.4180024034087532</v>
       </c>
       <c r="C446" t="n">
-        <v>0.4428082450650298</v>
+        <v>0.4428082450650297</v>
       </c>
       <c r="D446" t="n">
         <v>0.8380408653846154</v>
@@ -8169,7 +8169,7 @@
         <v>0.4123513035551231</v>
       </c>
       <c r="C456" t="n">
-        <v>0.4371048760485635</v>
+        <v>0.4371048760485636</v>
       </c>
       <c r="D456" t="n">
         <v>0.8419471153846154</v>
@@ -8203,7 +8203,7 @@
         <v>0.4112318692825823</v>
       </c>
       <c r="C458" t="n">
-        <v>0.4359740095750953</v>
+        <v>0.4359740095750952</v>
       </c>
       <c r="D458" t="n">
         <v>0.8419471153846154</v>
@@ -8234,7 +8234,7 @@
         <v>459</v>
       </c>
       <c r="B460" t="n">
-        <v>0.4101161530209229</v>
+        <v>0.4101161530209228</v>
       </c>
       <c r="C460" t="n">
         <v>0.4348465087371398</v>
@@ -8251,10 +8251,10 @@
         <v>460</v>
       </c>
       <c r="B461" t="n">
-        <v>0.4095597050039725</v>
+        <v>0.4095597050039724</v>
       </c>
       <c r="C461" t="n">
-        <v>0.4342840329105149</v>
+        <v>0.4342840329105148</v>
       </c>
       <c r="D461" t="n">
         <v>0.8425480769230769</v>
@@ -8268,7 +8268,7 @@
         <v>461</v>
       </c>
       <c r="B462" t="n">
-        <v>0.4090042053848827</v>
+        <v>0.4090042053848826</v>
       </c>
       <c r="C462" t="n">
         <v>0.4337224133623016</v>
@@ -8421,10 +8421,10 @@
         <v>470</v>
       </c>
       <c r="B471" t="n">
-        <v>0.4040483772294234</v>
+        <v>0.4040483772294232</v>
       </c>
       <c r="C471" t="n">
-        <v>0.4287071501855389</v>
+        <v>0.428707150185539</v>
       </c>
       <c r="D471" t="n">
         <v>0.8464543269230769</v>
@@ -8455,7 +8455,7 @@
         <v>472</v>
       </c>
       <c r="B473" t="n">
-        <v>0.4029580095809918</v>
+        <v>0.4029580095809916</v>
       </c>
       <c r="C473" t="n">
         <v>0.4276024564990846</v>
@@ -8594,7 +8594,7 @@
         <v>0.3986376263048135</v>
       </c>
       <c r="C481" t="n">
-        <v>0.4232204185140481</v>
+        <v>0.423220418514048</v>
       </c>
       <c r="D481" t="n">
         <v>0.8488581730769231</v>
@@ -8693,10 +8693,10 @@
         <v>486</v>
       </c>
       <c r="B487" t="n">
-        <v>0.3954415505149397</v>
+        <v>0.3954415505149396</v>
       </c>
       <c r="C487" t="n">
-        <v>0.419973310832274</v>
+        <v>0.4199733108322739</v>
       </c>
       <c r="D487" t="n">
         <v>0.8494591346153846</v>
@@ -8713,7 +8713,7 @@
         <v>0.3949126321814749</v>
       </c>
       <c r="C488" t="n">
-        <v>0.4194354721357791</v>
+        <v>0.419435472135779</v>
       </c>
       <c r="D488" t="n">
         <v>0.8494591346153846</v>
@@ -8730,7 +8730,7 @@
         <v>0.3943847990743115</v>
       </c>
       <c r="C489" t="n">
-        <v>0.4188985979063879</v>
+        <v>0.418898597906388</v>
       </c>
       <c r="D489" t="n">
         <v>0.8506610576923077</v>
@@ -8761,7 +8761,7 @@
         <v>490</v>
       </c>
       <c r="B491" t="n">
-        <v>0.3933324035687378</v>
+        <v>0.3933324035687376</v>
       </c>
       <c r="C491" t="n">
         <v>0.4178277548422121</v>
@@ -8778,10 +8778,10 @@
         <v>491</v>
       </c>
       <c r="B492" t="n">
-        <v>0.3928078484420127</v>
+        <v>0.3928078484420128</v>
       </c>
       <c r="C492" t="n">
-        <v>0.4172937918174771</v>
+        <v>0.4172937918174772</v>
       </c>
       <c r="D492" t="n">
         <v>0.8515625</v>
@@ -8883,7 +8883,7 @@
         <v>0.3896837281411757</v>
       </c>
       <c r="C498" t="n">
-        <v>0.4141106040129867</v>
+        <v>0.4141106040129866</v>
       </c>
       <c r="D498" t="n">
         <v>0.8515625</v>
@@ -8968,7 +8968,7 @@
         <v>0.3871110247747362</v>
       </c>
       <c r="C503" t="n">
-        <v>0.4114851812995409</v>
+        <v>0.4114851812995408</v>
       </c>
       <c r="D503" t="n">
         <v>0.8536658653846154</v>
@@ -9036,7 +9036,7 @@
         <v>0.3850732160285632</v>
       </c>
       <c r="C507" t="n">
-        <v>0.4094028632821344</v>
+        <v>0.4094028632821343</v>
       </c>
       <c r="D507" t="n">
         <v>0.8545673076923077</v>
@@ -9070,7 +9070,7 @@
         <v>0.3840611458959922</v>
       </c>
       <c r="C509" t="n">
-        <v>0.4083677516512348</v>
+        <v>0.4083677516512347</v>
       </c>
       <c r="D509" t="n">
         <v>0.8548677884615384</v>
@@ -9084,7 +9084,7 @@
         <v>509</v>
       </c>
       <c r="B510" t="n">
-        <v>0.3835568262850362</v>
+        <v>0.3835568262850361</v>
       </c>
       <c r="C510" t="n">
         <v>0.4078517133903811</v>
@@ -9101,10 +9101,10 @@
         <v>510</v>
       </c>
       <c r="B511" t="n">
-        <v>0.3830536526885466</v>
+        <v>0.3830536526885465</v>
       </c>
       <c r="C511" t="n">
-        <v>0.4073366888179661</v>
+        <v>0.407336688817966</v>
       </c>
       <c r="D511" t="n">
         <v>0.8557692307692307</v>
@@ -9203,10 +9203,10 @@
         <v>516</v>
       </c>
       <c r="B517" t="n">
-        <v>0.3800587644181443</v>
+        <v>0.3800587644181442</v>
       </c>
       <c r="C517" t="n">
-        <v>0.4042679024360749</v>
+        <v>0.4042679024360748</v>
       </c>
       <c r="D517" t="n">
         <v>0.8566706730769231</v>
@@ -9305,7 +9305,7 @@
         <v>522</v>
       </c>
       <c r="B523" t="n">
-        <v>0.3771054752257956</v>
+        <v>0.3771054752257955</v>
       </c>
       <c r="C523" t="n">
         <v>0.4012359027490022</v>
@@ -9359,7 +9359,7 @@
         <v>0.3756444904346489</v>
       </c>
       <c r="C526" t="n">
-        <v>0.3997337525979082</v>
+        <v>0.3997337525979081</v>
       </c>
       <c r="D526" t="n">
         <v>0.8599759615384616</v>
@@ -9390,7 +9390,7 @@
         <v>527</v>
       </c>
       <c r="B528" t="n">
-        <v>0.3746763102722354</v>
+        <v>0.3746763102722353</v>
       </c>
       <c r="C528" t="n">
         <v>0.3987374585396034</v>
@@ -9461,7 +9461,7 @@
         <v>0.3727539015215342</v>
       </c>
       <c r="C532" t="n">
-        <v>0.3967572160143577</v>
+        <v>0.3967572160143575</v>
       </c>
       <c r="D532" t="n">
         <v>0.8611778846153846</v>
@@ -9475,10 +9475,10 @@
         <v>532</v>
       </c>
       <c r="B533" t="n">
-        <v>0.3722762061229586</v>
+        <v>0.3722762061229585</v>
       </c>
       <c r="C533" t="n">
-        <v>0.3962647283173055</v>
+        <v>0.3962647283173054</v>
       </c>
       <c r="D533" t="n">
         <v>0.8614783653846154</v>
@@ -9512,7 +9512,7 @@
         <v>0.3713243025378493</v>
       </c>
       <c r="C535" t="n">
-        <v>0.3952828406652417</v>
+        <v>0.3952828406652416</v>
       </c>
       <c r="D535" t="n">
         <v>0.8617788461538461</v>
@@ -9563,7 +9563,7 @@
         <v>0.3699051604450995</v>
       </c>
       <c r="C538" t="n">
-        <v>0.3938177269338049</v>
+        <v>0.3938177269338048</v>
       </c>
       <c r="D538" t="n">
         <v>0.8626802884615384</v>
@@ -9679,10 +9679,10 @@
         <v>544</v>
       </c>
       <c r="B545" t="n">
-        <v>0.3666344148675305</v>
+        <v>0.3666344148675304</v>
       </c>
       <c r="C545" t="n">
-        <v>0.3904351052718618</v>
+        <v>0.3904351052718617</v>
       </c>
       <c r="D545" t="n">
         <v>0.86328125</v>
@@ -9750,7 +9750,7 @@
         <v>0.3647908455865155</v>
       </c>
       <c r="C549" t="n">
-        <v>0.3885247433914629</v>
+        <v>0.3885247433914628</v>
       </c>
       <c r="D549" t="n">
         <v>0.8638822115384616</v>
@@ -9798,7 +9798,7 @@
         <v>551</v>
       </c>
       <c r="B552" t="n">
-        <v>0.3634202521869476</v>
+        <v>0.3634202521869475</v>
       </c>
       <c r="C552" t="n">
         <v>0.3871027080992711</v>
@@ -9835,7 +9835,7 @@
         <v>0.3625122577041859</v>
       </c>
       <c r="C554" t="n">
-        <v>0.3861597841006364</v>
+        <v>0.3861597841006363</v>
       </c>
       <c r="D554" t="n">
         <v>0.8647836538461539</v>
@@ -9849,7 +9849,7 @@
         <v>554</v>
       </c>
       <c r="B555" t="n">
-        <v>0.3620599764585891</v>
+        <v>0.3620599764585892</v>
       </c>
       <c r="C555" t="n">
         <v>0.3856898490641274</v>
@@ -9917,7 +9917,7 @@
         <v>558</v>
       </c>
       <c r="B559" t="n">
-        <v>0.3602622546411119</v>
+        <v>0.3602622546411118</v>
       </c>
       <c r="C559" t="n">
         <v>0.3838202638225802</v>
@@ -10056,7 +10056,7 @@
         <v>0.3567211799736583</v>
       </c>
       <c r="C567" t="n">
-        <v>0.3801295864063471</v>
+        <v>0.380129586406347</v>
       </c>
       <c r="D567" t="n">
         <v>0.8662860576923077</v>
@@ -10138,7 +10138,7 @@
         <v>571</v>
       </c>
       <c r="B572" t="n">
-        <v>0.3545444590516473</v>
+        <v>0.3545444590516472</v>
       </c>
       <c r="C572" t="n">
         <v>0.3778554967086628</v>
@@ -10206,7 +10206,7 @@
         <v>575</v>
       </c>
       <c r="B576" t="n">
-        <v>0.3528230482465591</v>
+        <v>0.352823048246559</v>
       </c>
       <c r="C576" t="n">
         <v>0.3760541160665388</v>
@@ -10294,7 +10294,7 @@
         <v>0.3506959925094388</v>
       </c>
       <c r="C581" t="n">
-        <v>0.3738245783987303</v>
+        <v>0.3738245783987302</v>
       </c>
       <c r="D581" t="n">
         <v>0.8689903846153846</v>
@@ -10430,7 +10430,7 @@
         <v>0.3473490546150397</v>
       </c>
       <c r="C589" t="n">
-        <v>0.3703080655556878</v>
+        <v>0.3703080655556877</v>
       </c>
       <c r="D589" t="n">
         <v>0.8695913461538461</v>
@@ -10447,7 +10447,7 @@
         <v>0.3469355078038056</v>
       </c>
       <c r="C590" t="n">
-        <v>0.369872853165986</v>
+        <v>0.3698728531659859</v>
       </c>
       <c r="D590" t="n">
         <v>0.8695913461538461</v>
@@ -10461,7 +10461,7 @@
         <v>590</v>
       </c>
       <c r="B591" t="n">
-        <v>0.3465230229815012</v>
+        <v>0.3465230229815013</v>
       </c>
       <c r="C591" t="n">
         <v>0.3694386012570797</v>
@@ -10495,7 +10495,7 @@
         <v>592</v>
       </c>
       <c r="B593" t="n">
-        <v>0.345701227977951</v>
+        <v>0.3457012279779511</v>
       </c>
       <c r="C593" t="n">
         <v>0.3685729707972111</v>
@@ -10529,7 +10529,7 @@
         <v>594</v>
       </c>
       <c r="B595" t="n">
-        <v>0.3448836467510154</v>
+        <v>0.3448836467510153</v>
       </c>
       <c r="C595" t="n">
         <v>0.3677111578519477</v>
@@ -10563,7 +10563,7 @@
         <v>596</v>
       </c>
       <c r="B597" t="n">
-        <v>0.3440702561392252</v>
+        <v>0.3440702561392253</v>
       </c>
       <c r="C597" t="n">
         <v>0.3668531458600303</v>
@@ -10665,7 +10665,7 @@
         <v>602</v>
       </c>
       <c r="B603" t="n">
-        <v>0.3416549921930835</v>
+        <v>0.3416549921930836</v>
       </c>
       <c r="C603" t="n">
         <v>0.3643017467621401</v>
@@ -10685,7 +10685,7 @@
         <v>0.3412560491965592</v>
       </c>
       <c r="C604" t="n">
-        <v>0.3638797922765719</v>
+        <v>0.3638797922765718</v>
       </c>
       <c r="D604" t="n">
         <v>0.8701923076923077</v>
@@ -10699,10 +10699,10 @@
         <v>604</v>
       </c>
       <c r="B605" t="n">
-        <v>0.3408581269835407</v>
+        <v>0.3408581269835406</v>
       </c>
       <c r="C605" t="n">
-        <v>0.3634587687694917</v>
+        <v>0.3634587687694916</v>
       </c>
       <c r="D605" t="n">
         <v>0.8701923076923077</v>
@@ -10736,7 +10736,7 @@
         <v>0.3400653326698654</v>
       </c>
       <c r="C607" t="n">
-        <v>0.3626195059013481</v>
+        <v>0.3626195059013482</v>
       </c>
       <c r="D607" t="n">
         <v>0.8701923076923077</v>
@@ -10784,7 +10784,7 @@
         <v>609</v>
       </c>
       <c r="B610" t="n">
-        <v>0.3388837202835226</v>
+        <v>0.3388837202835225</v>
       </c>
       <c r="C610" t="n">
         <v>0.3613675387666445</v>
@@ -10988,7 +10988,7 @@
         <v>621</v>
       </c>
       <c r="B622" t="n">
-        <v>0.3342466270015551</v>
+        <v>0.3342466270015549</v>
       </c>
       <c r="C622" t="n">
         <v>0.3564416501663996</v>
@@ -11144,7 +11144,7 @@
         <v>0.3308602354460939</v>
       </c>
       <c r="C631" t="n">
-        <v>0.3528315860436531</v>
+        <v>0.352831586043653</v>
       </c>
       <c r="D631" t="n">
         <v>0.8716947115384616</v>
@@ -11212,7 +11212,7 @@
         <v>0.3293796340676359</v>
       </c>
       <c r="C635" t="n">
-        <v>0.3512498206858446</v>
+        <v>0.3512498206858445</v>
       </c>
       <c r="D635" t="n">
         <v>0.8719951923076923</v>
@@ -11226,7 +11226,7 @@
         <v>635</v>
       </c>
       <c r="B636" t="n">
-        <v>0.3290117982905588</v>
+        <v>0.3290117982905587</v>
       </c>
       <c r="C636" t="n">
         <v>0.350856535666956</v>
@@ -11263,7 +11263,7 @@
         <v>0.3282788817085516</v>
       </c>
       <c r="C638" t="n">
-        <v>0.3500725369375843</v>
+        <v>0.3500725369375842</v>
       </c>
       <c r="D638" t="n">
         <v>0.8722956730769231</v>
@@ -11277,7 +11277,7 @@
         <v>638</v>
       </c>
       <c r="B639" t="n">
-        <v>0.3279137944758093</v>
+        <v>0.3279137944758092</v>
       </c>
       <c r="C639" t="n">
         <v>0.349681818577708</v>
@@ -11294,7 +11294,7 @@
         <v>639</v>
       </c>
       <c r="B640" t="n">
-        <v>0.3275496169989646</v>
+        <v>0.3275496169989645</v>
       </c>
       <c r="C640" t="n">
         <v>0.3492919511225063</v>
@@ -11328,7 +11328,7 @@
         <v>641</v>
       </c>
       <c r="B642" t="n">
-        <v>0.3268239784746858</v>
+        <v>0.3268239784746857</v>
       </c>
       <c r="C642" t="n">
         <v>0.348514759636132</v>
@@ -11345,7 +11345,7 @@
         <v>642</v>
       </c>
       <c r="B643" t="n">
-        <v>0.3264625110134739</v>
+        <v>0.3264625110134738</v>
       </c>
       <c r="C643" t="n">
         <v>0.3481274309630114</v>
@@ -11484,7 +11484,7 @@
         <v>0.3236027923557555</v>
       </c>
       <c r="C651" t="n">
-        <v>0.3450589055729124</v>
+        <v>0.3450589055729122</v>
       </c>
       <c r="D651" t="n">
         <v>0.8731971153846154</v>
@@ -11549,7 +11549,7 @@
         <v>654</v>
       </c>
       <c r="B655" t="n">
-        <v>0.3221939491554655</v>
+        <v>0.3221939491554654</v>
       </c>
       <c r="C655" t="n">
         <v>0.3435444722606546</v>
@@ -11569,7 +11569,7 @@
         <v>0.3218438931976224</v>
       </c>
       <c r="C656" t="n">
-        <v>0.3431679046064853</v>
+        <v>0.3431679046064852</v>
       </c>
       <c r="D656" t="n">
         <v>0.8740985576923077</v>
@@ -11583,7 +11583,7 @@
         <v>656</v>
       </c>
       <c r="B657" t="n">
-        <v>0.3214946928723438</v>
+        <v>0.3214946928723437</v>
       </c>
       <c r="C657" t="n">
         <v>0.3427921486505685</v>
@@ -11654,7 +11654,7 @@
         <v>0.3201063851392947</v>
       </c>
       <c r="C661" t="n">
-        <v>0.3412971962881028</v>
+        <v>0.3412971962881027</v>
       </c>
       <c r="D661" t="n">
         <v>0.8743990384615384</v>
@@ -11668,7 +11668,7 @@
         <v>661</v>
       </c>
       <c r="B662" t="n">
-        <v>0.3197614159622084</v>
+        <v>0.3197614159622083</v>
       </c>
       <c r="C662" t="n">
         <v>0.3409254647185819</v>
@@ -11787,10 +11787,10 @@
         <v>668</v>
       </c>
       <c r="B669" t="n">
-        <v>0.3173698907516914</v>
+        <v>0.3173698907516913</v>
       </c>
       <c r="C669" t="n">
-        <v>0.3383455642866929</v>
+        <v>0.3383455642866928</v>
       </c>
       <c r="D669" t="n">
         <v>0.8759014423076923</v>
@@ -11855,7 +11855,7 @@
         <v>672</v>
       </c>
       <c r="B673" t="n">
-        <v>0.3160213090796028</v>
+        <v>0.3160213090796027</v>
       </c>
       <c r="C673" t="n">
         <v>0.3368885978086473</v>
@@ -11875,7 +11875,7 @@
         <v>0.3156861790660572</v>
       </c>
       <c r="C674" t="n">
-        <v>0.3365262956397193</v>
+        <v>0.3365262956397192</v>
       </c>
       <c r="D674" t="n">
         <v>0.8762019230769231</v>
@@ -11889,7 +11889,7 @@
         <v>674</v>
       </c>
       <c r="B675" t="n">
-        <v>0.3153518491618401</v>
+        <v>0.3153518491618402</v>
       </c>
       <c r="C675" t="n">
         <v>0.3361647648508846</v>
@@ -11909,7 +11909,7 @@
         <v>0.315018316355385</v>
       </c>
       <c r="C676" t="n">
-        <v>0.3358040032521094</v>
+        <v>0.3358040032521093</v>
       </c>
       <c r="D676" t="n">
         <v>0.8771033653846154</v>
@@ -11977,7 +11977,7 @@
         <v>0.3136920961781438</v>
       </c>
       <c r="C680" t="n">
-        <v>0.3343686051638846</v>
+        <v>0.3343686051638845</v>
       </c>
       <c r="D680" t="n">
         <v>0.8771033653846154</v>
@@ -11994,7 +11994,7 @@
         <v>0.3133625039908404</v>
       </c>
       <c r="C681" t="n">
-        <v>0.3340116568729247</v>
+        <v>0.3340116568729246</v>
       </c>
       <c r="D681" t="n">
         <v>0.8771033653846154</v>
@@ -12011,7 +12011,7 @@
         <v>0.3130336910157267</v>
       </c>
       <c r="C682" t="n">
-        <v>0.333655464757683</v>
+        <v>0.3336554647576831</v>
       </c>
       <c r="D682" t="n">
         <v>0.8771033653846154</v>
@@ -12062,7 +12062,7 @@
         <v>0.3120518979171064</v>
       </c>
       <c r="C685" t="n">
-        <v>0.3325914040241373</v>
+        <v>0.3325914040241372</v>
       </c>
       <c r="D685" t="n">
         <v>0.8774038461538461</v>
@@ -12178,10 +12178,10 @@
         <v>691</v>
       </c>
       <c r="B692" t="n">
-        <v>0.3097877737636968</v>
+        <v>0.3097877737636966</v>
       </c>
       <c r="C692" t="n">
-        <v>0.3301346640399739</v>
+        <v>0.3301346640399738</v>
       </c>
       <c r="D692" t="n">
         <v>0.8792067307692307</v>
@@ -12198,7 +12198,7 @@
         <v>0.3094673395587995</v>
       </c>
       <c r="C693" t="n">
-        <v>0.3297866495588424</v>
+        <v>0.3297866495588423</v>
       </c>
       <c r="D693" t="n">
         <v>0.8792067307692307</v>
@@ -12215,7 +12215,7 @@
         <v>0.309147649807435</v>
       </c>
       <c r="C694" t="n">
-        <v>0.3294393659174497</v>
+        <v>0.3294393659174498</v>
       </c>
       <c r="D694" t="n">
         <v>0.8792067307692307</v>
@@ -12229,7 +12229,7 @@
         <v>694</v>
       </c>
       <c r="B695" t="n">
-        <v>0.308828701677458</v>
+        <v>0.3088287016774579</v>
       </c>
       <c r="C695" t="n">
         <v>0.3290928110484466</v>
@@ -12280,7 +12280,7 @@
         <v>697</v>
       </c>
       <c r="B698" t="n">
-        <v>0.3078762788484342</v>
+        <v>0.3078762788484341</v>
       </c>
       <c r="C698" t="n">
         <v>0.3280574985072117</v>
@@ -12317,7 +12317,7 @@
         <v>0.3072449869438465</v>
       </c>
       <c r="C700" t="n">
-        <v>0.3273708964227796</v>
+        <v>0.3273708964227795</v>
       </c>
       <c r="D700" t="n">
         <v>0.8798076923076923</v>
@@ -12331,7 +12331,7 @@
         <v>700</v>
       </c>
       <c r="B701" t="n">
-        <v>0.3069304296450973</v>
+        <v>0.3069304296450972</v>
       </c>
       <c r="C701" t="n">
         <v>0.3270286711672906</v>
@@ -12402,7 +12402,7 @@
         <v>0.3056793938839394</v>
       </c>
       <c r="C705" t="n">
-        <v>0.325666895060961</v>
+        <v>0.3256668950609609</v>
       </c>
       <c r="D705" t="n">
         <v>0.8795072115384616</v>
@@ -12416,7 +12416,7 @@
         <v>705</v>
       </c>
       <c r="B706" t="n">
-        <v>0.3053684196397548</v>
+        <v>0.3053684196397547</v>
       </c>
       <c r="C706" t="n">
         <v>0.3253282222651835</v>
@@ -12450,7 +12450,7 @@
         <v>707</v>
       </c>
       <c r="B708" t="n">
-        <v>0.3047485938103396</v>
+        <v>0.3047485938103395</v>
       </c>
       <c r="C708" t="n">
         <v>0.3246529882553872</v>
@@ -12504,7 +12504,7 @@
         <v>0.3038241214576736</v>
       </c>
       <c r="C711" t="n">
-        <v>0.323645386695055</v>
+        <v>0.3236453866950549</v>
       </c>
       <c r="D711" t="n">
         <v>0.8795072115384616</v>
@@ -12518,10 +12518,10 @@
         <v>711</v>
       </c>
       <c r="B712" t="n">
-        <v>0.3035173577196269</v>
+        <v>0.3035173577196268</v>
       </c>
       <c r="C712" t="n">
-        <v>0.3233109115478082</v>
+        <v>0.3233109115478081</v>
       </c>
       <c r="D712" t="n">
         <v>0.8795072115384616</v>
@@ -12552,10 +12552,10 @@
         <v>713</v>
       </c>
       <c r="B714" t="n">
-        <v>0.3029059049577157</v>
+        <v>0.3029059049577156</v>
       </c>
       <c r="C714" t="n">
-        <v>0.3226440376791635</v>
+        <v>0.3226440376791634</v>
       </c>
       <c r="D714" t="n">
         <v>0.8795072115384616</v>
@@ -12572,7 +12572,7 @@
         <v>0.3026012106875967</v>
       </c>
       <c r="C715" t="n">
-        <v>0.3223116351059998</v>
+        <v>0.3223116351059997</v>
       </c>
       <c r="D715" t="n">
         <v>0.8795072115384616</v>
@@ -12691,7 +12691,7 @@
         <v>0.300487374903923</v>
       </c>
       <c r="C722" t="n">
-        <v>0.320003947337999</v>
+        <v>0.3200039473379989</v>
       </c>
       <c r="D722" t="n">
         <v>0.8795072115384616</v>
@@ -12742,7 +12742,7 @@
         <v>0.2995914961898034</v>
       </c>
       <c r="C725" t="n">
-        <v>0.3190250831862738</v>
+        <v>0.3190250831862737</v>
       </c>
       <c r="D725" t="n">
         <v>0.8795072115384616</v>
@@ -12892,7 +12892,7 @@
         <v>733</v>
       </c>
       <c r="B734" t="n">
-        <v>0.2969391885025574</v>
+        <v>0.2969391885025573</v>
       </c>
       <c r="C734" t="n">
         <v>0.3161243818920782</v>
@@ -12977,7 +12977,7 @@
         <v>738</v>
       </c>
       <c r="B739" t="n">
-        <v>0.2954881001094731</v>
+        <v>0.295488100109473</v>
       </c>
       <c r="C739" t="n">
         <v>0.3145357872809787</v>
@@ -12997,7 +12997,7 @@
         <v>0.2951997680932423</v>
       </c>
       <c r="C740" t="n">
-        <v>0.3142200052681653</v>
+        <v>0.3142200052681652</v>
       </c>
       <c r="D740" t="n">
         <v>0.8795072115384616</v>
@@ -13116,7 +13116,7 @@
         <v>0.2931987623520251</v>
       </c>
       <c r="C747" t="n">
-        <v>0.3120273998309182</v>
+        <v>0.312027399830918</v>
       </c>
       <c r="D747" t="n">
         <v>0.8807091346153846</v>
@@ -13181,7 +13181,7 @@
         <v>750</v>
       </c>
       <c r="B751" t="n">
-        <v>0.2920687381500359</v>
+        <v>0.2920687381500358</v>
       </c>
       <c r="C751" t="n">
         <v>0.3107883731374574</v>
@@ -13402,7 +13402,7 @@
         <v>763</v>
       </c>
       <c r="B764" t="n">
-        <v>0.2884615596456065</v>
+        <v>0.2884615596456064</v>
       </c>
       <c r="C764" t="n">
         <v>0.3068298491999794</v>
@@ -13422,7 +13422,7 @@
         <v>0.2881881380257633</v>
       </c>
       <c r="C765" t="n">
-        <v>0.3065296075395534</v>
+        <v>0.3065296075395533</v>
       </c>
       <c r="D765" t="n">
         <v>0.8816105769230769</v>
@@ -13439,7 +13439,7 @@
         <v>0.2879152851279037</v>
       </c>
       <c r="C766" t="n">
-        <v>0.3062299666268255</v>
+        <v>0.3062299666268256</v>
       </c>
       <c r="D766" t="n">
         <v>0.8816105769230769</v>
@@ -13456,7 +13456,7 @@
         <v>0.2876429989222668</v>
       </c>
       <c r="C767" t="n">
-        <v>0.3059309249193116</v>
+        <v>0.3059309249193115</v>
       </c>
       <c r="D767" t="n">
         <v>0.8816105769230769</v>
@@ -13473,7 +13473,7 @@
         <v>0.2873712773901141</v>
       </c>
       <c r="C768" t="n">
-        <v>0.3056324808812785</v>
+        <v>0.3056324808812784</v>
       </c>
       <c r="D768" t="n">
         <v>0.8819110576923077</v>
@@ -13606,10 +13606,10 @@
         <v>775</v>
       </c>
       <c r="B776" t="n">
-        <v>0.2852175947461436</v>
+        <v>0.2852175947461435</v>
       </c>
       <c r="C776" t="n">
-        <v>0.3032662625917052</v>
+        <v>0.3032662625917051</v>
       </c>
       <c r="D776" t="n">
         <v>0.8822115384615384</v>
@@ -13643,7 +13643,7 @@
         <v>0.2846846828153891</v>
       </c>
       <c r="C778" t="n">
-        <v>0.302680579220728</v>
+        <v>0.3026805792207279</v>
       </c>
       <c r="D778" t="n">
         <v>0.8822115384615384</v>
@@ -13745,7 +13745,7 @@
         <v>0.2830989234783902</v>
       </c>
       <c r="C784" t="n">
-        <v>0.3009374318002227</v>
+        <v>0.3009374318002226</v>
       </c>
       <c r="D784" t="n">
         <v>0.8822115384615384</v>
@@ -13776,10 +13776,10 @@
         <v>785</v>
       </c>
       <c r="B786" t="n">
-        <v>0.2825746128595468</v>
+        <v>0.2825746128595467</v>
       </c>
       <c r="C786" t="n">
-        <v>0.3003609784408453</v>
+        <v>0.3003609784408452</v>
       </c>
       <c r="D786" t="n">
         <v>0.8822115384615384</v>
@@ -13793,7 +13793,7 @@
         <v>786</v>
       </c>
       <c r="B787" t="n">
-        <v>0.2823132510180683</v>
+        <v>0.2823132510180682</v>
       </c>
       <c r="C787" t="n">
         <v>0.3000736070577548</v>
@@ -13847,7 +13847,7 @@
         <v>0.281532317741709</v>
       </c>
       <c r="C790" t="n">
-        <v>0.2992148972127447</v>
+        <v>0.2992148972127446</v>
       </c>
       <c r="D790" t="n">
         <v>0.8834134615384616</v>
@@ -14014,7 +14014,7 @@
         <v>799</v>
       </c>
       <c r="B800" t="n">
-        <v>0.278962822012453</v>
+        <v>0.2789628220124529</v>
       </c>
       <c r="C800" t="n">
         <v>0.2963889913786513</v>
@@ -14034,7 +14034,7 @@
         <v>0.278708672576605</v>
       </c>
       <c r="C801" t="n">
-        <v>0.2961094509387006</v>
+        <v>0.2961094509387005</v>
       </c>
       <c r="D801" t="n">
         <v>0.8846153846153846</v>
@@ -14085,7 +14085,7 @@
         <v>0.2779492319027054</v>
       </c>
       <c r="C804" t="n">
-        <v>0.2952741195682046</v>
+        <v>0.2952741195682045</v>
       </c>
       <c r="D804" t="n">
         <v>0.8855168269230769</v>
@@ -14116,7 +14116,7 @@
         <v>805</v>
       </c>
       <c r="B806" t="n">
-        <v>0.2774454280651123</v>
+        <v>0.2774454280651122</v>
       </c>
       <c r="C806" t="n">
         <v>0.2947199604409551</v>
@@ -14323,7 +14323,7 @@
         <v>0.2744636750724427</v>
       </c>
       <c r="C818" t="n">
-        <v>0.2914402276321798</v>
+        <v>0.2914402276321799</v>
       </c>
       <c r="D818" t="n">
         <v>0.8879206730769231</v>
@@ -14354,7 +14354,7 @@
         <v>819</v>
       </c>
       <c r="B820" t="n">
-        <v>0.2739734451683138</v>
+        <v>0.2739734451683137</v>
       </c>
       <c r="C820" t="n">
         <v>0.2909010475888769</v>
@@ -14391,7 +14391,7 @@
         <v>0.273485105522575</v>
       </c>
       <c r="C822" t="n">
-        <v>0.2903639671926076</v>
+        <v>0.2903639671926075</v>
       </c>
       <c r="D822" t="n">
         <v>0.8885216346153846</v>
@@ -14439,10 +14439,10 @@
         <v>824</v>
       </c>
       <c r="B825" t="n">
-        <v>0.2727561145350241</v>
+        <v>0.272756114535024</v>
       </c>
       <c r="C825" t="n">
-        <v>0.2895622619348166</v>
+        <v>0.2895622619348165</v>
       </c>
       <c r="D825" t="n">
         <v>0.8885216346153846</v>
@@ -14456,7 +14456,7 @@
         <v>825</v>
       </c>
       <c r="B826" t="n">
-        <v>0.2725140499833724</v>
+        <v>0.2725140499833723</v>
       </c>
       <c r="C826" t="n">
         <v>0.2892960660581806</v>
@@ -14473,7 +14473,7 @@
         <v>826</v>
       </c>
       <c r="B827" t="n">
-        <v>0.2722724492547783</v>
+        <v>0.2722724492547782</v>
       </c>
       <c r="C827" t="n">
         <v>0.2890303877648568</v>
@@ -14595,7 +14595,7 @@
         <v>0.2705941123967618</v>
       </c>
       <c r="C834" t="n">
-        <v>0.287185031186797</v>
+        <v>0.2871850311867971</v>
       </c>
       <c r="D834" t="n">
         <v>0.8888221153846154</v>
@@ -14711,7 +14711,7 @@
         <v>840</v>
       </c>
       <c r="B841" t="n">
-        <v>0.2689379564263452</v>
+        <v>0.2689379564263451</v>
       </c>
       <c r="C841" t="n">
         <v>0.2853645692917092</v>
@@ -14847,7 +14847,7 @@
         <v>848</v>
       </c>
       <c r="B849" t="n">
-        <v>0.2670717788665177</v>
+        <v>0.2670717788665178</v>
       </c>
       <c r="C849" t="n">
         <v>0.2833140122840582</v>
@@ -14898,7 +14898,7 @@
         <v>851</v>
       </c>
       <c r="B852" t="n">
-        <v>0.2663791419275485</v>
+        <v>0.2663791419275484</v>
       </c>
       <c r="C852" t="n">
         <v>0.2825531821734441</v>
@@ -14949,7 +14949,7 @@
         <v>854</v>
       </c>
       <c r="B855" t="n">
-        <v>0.2656903685646423</v>
+        <v>0.2656903685646422</v>
       </c>
       <c r="C855" t="n">
         <v>0.2817967385794221</v>
@@ -15034,7 +15034,7 @@
         <v>859</v>
       </c>
       <c r="B860" t="n">
-        <v>0.2645509092226854</v>
+        <v>0.2645509092226853</v>
       </c>
       <c r="C860" t="n">
         <v>0.2805456653688496</v>
@@ -15071,7 +15071,7 @@
         <v>0.2640980712074975</v>
       </c>
       <c r="C862" t="n">
-        <v>0.2800485934275975</v>
+        <v>0.2800485934275974</v>
       </c>
       <c r="D862" t="n">
         <v>0.8891225961538461</v>
@@ -15119,10 +15119,10 @@
         <v>864</v>
       </c>
       <c r="B865" t="n">
-        <v>0.2634219408592288</v>
+        <v>0.2634219408592287</v>
       </c>
       <c r="C865" t="n">
-        <v>0.2793065552319826</v>
+        <v>0.2793065552319825</v>
       </c>
       <c r="D865" t="n">
         <v>0.8897235576923077</v>
@@ -15153,7 +15153,7 @@
         <v>866</v>
       </c>
       <c r="B867" t="n">
-        <v>0.2629732582110808</v>
+        <v>0.2629732582110807</v>
       </c>
       <c r="C867" t="n">
         <v>0.2788142301910492</v>
@@ -15306,7 +15306,7 @@
         <v>875</v>
       </c>
       <c r="B876" t="n">
-        <v>0.2609744258173812</v>
+        <v>0.2609744258173811</v>
       </c>
       <c r="C876" t="n">
         <v>0.2766219518269621</v>
@@ -15374,7 +15374,7 @@
         <v>879</v>
       </c>
       <c r="B880" t="n">
-        <v>0.2600965422145825</v>
+        <v>0.2600965422145824</v>
       </c>
       <c r="C880" t="n">
         <v>0.2756596440776407</v>
@@ -15476,7 +15476,7 @@
         <v>885</v>
       </c>
       <c r="B886" t="n">
-        <v>0.2587916104606001</v>
+        <v>0.2587916104606</v>
       </c>
       <c r="C886" t="n">
         <v>0.2742298707292805</v>
@@ -15493,10 +15493,10 @@
         <v>886</v>
       </c>
       <c r="B887" t="n">
-        <v>0.2585754958319851</v>
+        <v>0.258575495831985</v>
       </c>
       <c r="C887" t="n">
-        <v>0.2739931586053093</v>
+        <v>0.2739931586053092</v>
       </c>
       <c r="D887" t="n">
         <v>0.8927283653846154</v>
@@ -15544,7 +15544,7 @@
         <v>889</v>
       </c>
       <c r="B890" t="n">
-        <v>0.2579294865075168</v>
+        <v>0.2579294865075167</v>
       </c>
       <c r="C890" t="n">
         <v>0.2732857157121277</v>
@@ -15581,7 +15581,7 @@
         <v>0.257500748794785</v>
       </c>
       <c r="C892" t="n">
-        <v>0.2728163212359697</v>
+        <v>0.2728163212359696</v>
       </c>
       <c r="D892" t="n">
         <v>0.8927283653846154</v>
@@ -15649,7 +15649,7 @@
         <v>0.2566478810894118</v>
       </c>
       <c r="C896" t="n">
-        <v>0.2718828566860251</v>
+        <v>0.2718828566860252</v>
       </c>
       <c r="D896" t="n">
         <v>0.8939302884615384</v>
@@ -15700,7 +15700,7 @@
         <v>0.2560122303500972</v>
       </c>
       <c r="C899" t="n">
-        <v>0.2711873844499914</v>
+        <v>0.2711873844499913</v>
       </c>
       <c r="D899" t="n">
         <v>0.8951322115384616</v>
@@ -15819,7 +15819,7 @@
         <v>0.2545422168381736</v>
       </c>
       <c r="C906" t="n">
-        <v>0.2695798678509831</v>
+        <v>0.269579867850983</v>
       </c>
       <c r="D906" t="n">
         <v>0.8957331730769231</v>
@@ -15887,7 +15887,7 @@
         <v>0.2537103882825423</v>
       </c>
       <c r="C910" t="n">
-        <v>0.2686707684026054</v>
+        <v>0.2686707684026053</v>
       </c>
       <c r="D910" t="n">
         <v>0.8957331730769231</v>
@@ -15921,7 +15921,7 @@
         <v>0.2532966796950758</v>
       </c>
       <c r="C912" t="n">
-        <v>0.2682187779321353</v>
+        <v>0.2682187779321352</v>
       </c>
       <c r="D912" t="n">
         <v>0.8963341346153846</v>
@@ -15938,7 +15938,7 @@
         <v>0.2530903734996204</v>
       </c>
       <c r="C913" t="n">
-        <v>0.2679934189419634</v>
+        <v>0.2679934189419633</v>
       </c>
       <c r="D913" t="n">
         <v>0.8963341346153846</v>
@@ -16037,7 +16037,7 @@
         <v>918</v>
       </c>
       <c r="B919" t="n">
-        <v>0.2518601504916009</v>
+        <v>0.2518601504916008</v>
       </c>
       <c r="C919" t="n">
         <v>0.2666501084001069</v>
@@ -16074,7 +16074,7 @@
         <v>0.2514529544258623</v>
       </c>
       <c r="C921" t="n">
-        <v>0.2662056828027888</v>
+        <v>0.2662056828027887</v>
       </c>
       <c r="D921" t="n">
         <v>0.8990384615384616</v>
@@ -16108,7 +16108,7 @@
         <v>0.2510471851737225</v>
       </c>
       <c r="C923" t="n">
-        <v>0.2657629160140827</v>
+        <v>0.2657629160140826</v>
       </c>
       <c r="D923" t="n">
         <v>0.9005408653846154</v>
@@ -16292,7 +16292,7 @@
         <v>933</v>
       </c>
       <c r="B934" t="n">
-        <v>0.2488406331353702</v>
+        <v>0.2488406331353701</v>
       </c>
       <c r="C934" t="n">
         <v>0.2633569900745358</v>
@@ -16329,7 +16329,7 @@
         <v>0.248443961333548</v>
       </c>
       <c r="C936" t="n">
-        <v>0.2629248095342603</v>
+        <v>0.2629248095342602</v>
       </c>
       <c r="D936" t="n">
         <v>0.9026442307692307</v>
@@ -16414,7 +16414,7 @@
         <v>0.24745827245921</v>
       </c>
       <c r="C941" t="n">
-        <v>0.2618513348859174</v>
+        <v>0.2618513348859173</v>
       </c>
       <c r="D941" t="n">
         <v>0.9029447115384616</v>
@@ -16496,7 +16496,7 @@
         <v>945</v>
       </c>
       <c r="B946" t="n">
-        <v>0.2464810540255554</v>
+        <v>0.2464810540255553</v>
       </c>
       <c r="C946" t="n">
         <v>0.2607877276916875</v>
@@ -16567,7 +16567,7 @@
         <v>0.2457053050861392</v>
       </c>
       <c r="C950" t="n">
-        <v>0.2599438634512896</v>
+        <v>0.2599438634512895</v>
       </c>
       <c r="D950" t="n">
         <v>0.9044471153846154</v>
@@ -16598,7 +16598,7 @@
         <v>951</v>
       </c>
       <c r="B952" t="n">
-        <v>0.2453194202937094</v>
+        <v>0.2453194202937093</v>
       </c>
       <c r="C952" t="n">
         <v>0.2595242501739352</v>
@@ -16785,7 +16785,7 @@
         <v>962</v>
       </c>
       <c r="B963" t="n">
-        <v>0.2432204198102274</v>
+        <v>0.2432204198102273</v>
       </c>
       <c r="C963" t="n">
         <v>0.257243613501988</v>
@@ -16904,7 +16904,7 @@
         <v>969</v>
       </c>
       <c r="B970" t="n">
-        <v>0.2419049277173239</v>
+        <v>0.2419049277173238</v>
       </c>
       <c r="C970" t="n">
         <v>0.2558158896391935</v>
@@ -16921,7 +16921,7 @@
         <v>970</v>
       </c>
       <c r="B971" t="n">
-        <v>0.2417182640260238</v>
+        <v>0.2417182640260239</v>
       </c>
       <c r="C971" t="n">
         <v>0.2556134024423302</v>
@@ -16989,7 +16989,7 @@
         <v>974</v>
       </c>
       <c r="B975" t="n">
-        <v>0.2409747357976752</v>
+        <v>0.2409747357976751</v>
       </c>
       <c r="C975" t="n">
         <v>0.2548070987520261</v>
@@ -17179,7 +17179,7 @@
         <v>0.2389554700493752</v>
       </c>
       <c r="C986" t="n">
-        <v>0.2526194182150981</v>
+        <v>0.2526194182150982</v>
       </c>
       <c r="D986" t="n">
         <v>0.9053485576923077</v>
@@ -17264,7 +17264,7 @@
         <v>0.2380497409405777</v>
       </c>
       <c r="C991" t="n">
-        <v>0.2516391452084067</v>
+        <v>0.2516391452084066</v>
       </c>
       <c r="D991" t="n">
         <v>0.9053485576923077</v>
@@ -17295,7 +17295,7 @@
         <v>992</v>
       </c>
       <c r="B993" t="n">
-        <v>0.2376895367838369</v>
+        <v>0.2376895367838368</v>
       </c>
       <c r="C993" t="n">
         <v>0.2512494691697022</v>
@@ -17315,7 +17315,7 @@
         <v>0.2375098788817847</v>
       </c>
       <c r="C994" t="n">
-        <v>0.2510551488526154</v>
+        <v>0.2510551488526153</v>
       </c>
       <c r="D994" t="n">
         <v>0.9056490384615384</v>
